--- a/12608986.xlsx
+++ b/12608986.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c771313384576c48/Desktop/new_git/python-minor-project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{770A47B9-7D91-4BF9-8149-B810B1819792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8342317-6930-4539-825D-0F6A5315FD23}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="8_{770A47B9-7D91-4BF9-8149-B810B1819792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C413AEE3-11F8-424D-BF59-F7D7E5E27074}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
     <sheet name="Daily Log" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1027,10 +1027,10 @@
         <v>46241</v>
       </c>
       <c r="B7" s="9">
-        <v>480</v>
+        <v>420</v>
       </c>
       <c r="C7" s="9">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D7" s="9">
         <v>60</v>
@@ -1049,11 +1049,11 @@
       </c>
       <c r="I7" s="10">
         <f t="shared" si="0"/>
-        <v>900</v>
+        <v>825</v>
       </c>
       <c r="J7" s="10">
         <f t="shared" si="1"/>
-        <v>540</v>
+        <v>615</v>
       </c>
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
@@ -1068,7 +1068,7 @@
         <v>480</v>
       </c>
       <c r="C8" s="9">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
@@ -1081,11 +1081,11 @@
       <c r="H8" s="9"/>
       <c r="I8" s="10">
         <f t="shared" si="0"/>
-        <v>540</v>
+        <v>510</v>
       </c>
       <c r="J8" s="10">
         <f t="shared" si="1"/>
-        <v>900</v>
+        <v>930</v>
       </c>
       <c r="K8" s="11"/>
       <c r="L8" s="11"/>
@@ -1096,7 +1096,9 @@
       <c r="A9" s="8">
         <v>46243</v>
       </c>
-      <c r="B9" s="9"/>
+      <c r="B9" s="9">
+        <v>480</v>
+      </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
@@ -1107,13 +1109,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="9"/>
-      <c r="I9" s="10" t="str">
+      <c r="I9" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="10" t="str">
+        <v>480</v>
+      </c>
+      <c r="J9" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>960</v>
       </c>
       <c r="K9" s="11"/>
       <c r="L9" s="11"/>
@@ -1124,7 +1126,9 @@
       <c r="A10" s="8">
         <v>46244</v>
       </c>
-      <c r="B10" s="9"/>
+      <c r="B10" s="9">
+        <v>420</v>
+      </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
@@ -1137,11 +1141,11 @@
       <c r="H10" s="9"/>
       <c r="I10" s="10">
         <f t="shared" si="0"/>
-        <v>350</v>
+        <v>770</v>
       </c>
       <c r="J10" s="10">
         <f t="shared" si="1"/>
-        <v>1090</v>
+        <v>670</v>
       </c>
       <c r="K10" s="11"/>
       <c r="L10" s="11"/>
